--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="M82" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>6.16</v>
+        <v>2.5</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G101" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>6.16</v>
+        <v>2.5</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G97" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G97" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL104"/>
+  <dimension ref="A1:AL107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2349,27 +2349,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.45833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>1.21</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45877.54166666666</v>
+        <v>45877.5</v>
       </c>
     </row>
     <row r="25">
@@ -3669,27 +3669,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45877.54166666666</v>
+        <v>45877.5</v>
       </c>
     </row>
     <row r="26">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45877.54166666666</v>
+        <v>45877.5</v>
       </c>
     </row>
     <row r="27">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5121,27 +5121,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="39">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="40">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="41">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="42">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -6045,27 +6045,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="AL50" s="3" t="n">
-        <v>45877.61458333334</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="51">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="52">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="53">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="AL53" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.61458333334</v>
       </c>
     </row>
     <row r="54">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="AL61" s="3" t="n">
-        <v>45877.63541666666</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="62">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="63">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="AL63" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="64">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="AL64" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.63541666666</v>
       </c>
     </row>
     <row r="65">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9345,27 +9345,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="69">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="70">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.46</v>
+        <v>6.2</v>
       </c>
       <c r="M70" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>6.16</v>
+        <v>1.51</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
         <v>1.9</v>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="71">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N80" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11457,12 +11457,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="AL84" s="3" t="n">
-        <v>45877.66666666666</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="85">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="M85" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N85" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="AL85" s="3" t="n">
-        <v>45877.66666666666</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="86">
@@ -11721,27 +11721,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>45877.67708333334</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="87">
@@ -11853,27 +11853,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="88">
@@ -11985,27 +11985,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="AL88" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="89">
@@ -12117,27 +12117,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="AL89" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.67708333334</v>
       </c>
     </row>
     <row r="90">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="AL98" s="3" t="n">
-        <v>45877.83333333334</v>
+        <v>45877.79166666666</v>
       </c>
     </row>
     <row r="99">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="AL99" s="3" t="n">
-        <v>45877.85416666666</v>
+        <v>45877.79166666666</v>
       </c>
     </row>
     <row r="100">
@@ -13569,12 +13569,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="AL100" s="3" t="n">
-        <v>45877.875</v>
+        <v>45877.79166666666</v>
       </c>
     </row>
     <row r="101">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45877.875</v>
+        <v>45877.83333333334</v>
       </c>
     </row>
     <row r="102">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45877.89583333334</v>
+        <v>45877.85416666666</v>
       </c>
     </row>
     <row r="103">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14088,7 +14088,7 @@
         </is>
       </c>
       <c r="AL103" s="3" t="n">
-        <v>45877.89930555555</v>
+        <v>45877.875</v>
       </c>
     </row>
     <row r="104">
@@ -14097,129 +14097,525 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Minnesota United II</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Sporting KC II</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL104" s="3" t="n">
+        <v>45877.875</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>North Texas</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL105" s="3" t="n">
+        <v>45877.89583333334</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL106" s="3" t="n">
+        <v>45877.89930555555</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="inlineStr">
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL104" s="3" t="n">
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL107" s="3" t="n">
         <v>45877.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>15</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>1.21</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="M80" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="N80" t="n">
-        <v>2.7</v>
+        <v>6.16</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="M83" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N83" t="n">
-        <v>6.16</v>
+        <v>2.5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="M85" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N85" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC85" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>1.67</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G100" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>1.21</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.46</v>
+        <v>2.4</v>
       </c>
       <c r="M80" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N80" t="n">
-        <v>6.16</v>
+        <v>2.7</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G100" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
         <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G100" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL107"/>
+  <dimension ref="A1:AL105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>1.21</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="87">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11985,12 +11985,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="AL88" s="3" t="n">
-        <v>45877.66666666666</v>
+        <v>45877.67708333334</v>
       </c>
     </row>
     <row r="89">
@@ -12117,27 +12117,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="AL89" s="3" t="n">
-        <v>45877.67708333334</v>
+        <v>45877.79166666666</v>
       </c>
     </row>
     <row r="90">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13569,12 +13569,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="AL100" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.83333333334</v>
       </c>
     </row>
     <row r="101">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45877.83333333334</v>
+        <v>45877.85416666666</v>
       </c>
     </row>
     <row r="102">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45877.85416666666</v>
+        <v>45877.875</v>
       </c>
     </row>
     <row r="103">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="AL104" s="3" t="n">
-        <v>45877.875</v>
+        <v>45877.89583333334</v>
       </c>
     </row>
     <row r="105">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14352,270 +14352,6 @@
         </is>
       </c>
       <c r="AL105" s="3" t="n">
-        <v>45877.89583333334</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>45877</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL106" s="3" t="n">
-        <v>45877.89930555555</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>45877</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL107" s="3" t="n">
         <v>45877.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL105"/>
+  <dimension ref="A1:AL106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>3.95</v>
+        <v>3.62</v>
       </c>
       <c r="N4" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45877.45833333334</v>
+        <v>45877.5</v>
       </c>
     </row>
     <row r="17">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
         <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3537,27 +3537,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3669,27 +3669,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3801,27 +3801,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5121,27 +5121,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45877.54166666666</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45877.54166666666</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="38">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45877.54166666666</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="39">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -6045,27 +6045,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.61458333334</v>
       </c>
     </row>
     <row r="53">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="AL53" s="3" t="n">
-        <v>45877.61458333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="54">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="AL63" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.63541666666</v>
       </c>
     </row>
     <row r="64">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="AL64" s="3" t="n">
-        <v>45877.63541666666</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="65">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="71">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="M84" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>6.16</v>
+        <v>2.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14229,129 +14229,261 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL105" s="3" t="n">
+        <v>45877.89930555555</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="inlineStr">
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL105" s="3" t="n">
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL106" s="3" t="n">
         <v>45877.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>15</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.21</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.02</v>
+        <v>1.46</v>
       </c>
       <c r="M75" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N75" t="n">
-        <v>3.04</v>
+        <v>6.16</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N84" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC84" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>1.67</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G103" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45877.45833333334</v>
+        <v>45877.5</v>
       </c>
     </row>
     <row r="16">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>15</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45877.54166666666</v>
+        <v>45877.55208333334</v>
       </c>
     </row>
     <row r="36">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G98" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N4" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N64" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G99" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="M42" t="n">
         <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N67" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="M73" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="N73" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G99" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N4" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.81</v>
+        <v>3.17</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.17</v>
+        <v>3.81</v>
       </c>
       <c r="M38" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="M71" t="n">
-        <v>3.31</v>
+        <v>3.99</v>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>5.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G103" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
         <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.81</v>
+        <v>3.17</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.97</v>
+        <v>1.43</v>
       </c>
       <c r="M76" t="n">
-        <v>3.67</v>
+        <v>3.99</v>
       </c>
       <c r="N76" t="n">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G103" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N4" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
         <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M44" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N68" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G99" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL106"/>
+  <dimension ref="A1:AL104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45877.45833333334</v>
+        <v>45877.5</v>
       </c>
     </row>
     <row r="15">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>1.21</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4857,27 +4857,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45877.54166666666</v>
+        <v>45877.55208333334</v>
       </c>
     </row>
     <row r="35">
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45877.55208333334</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="36">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="M41" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.61458333334</v>
       </c>
     </row>
     <row r="52">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>45877.61458333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="53">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.63541666666</v>
       </c>
     </row>
     <row r="63">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="AL63" s="3" t="n">
-        <v>45877.63541666666</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="64">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="M69" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="N69" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="70">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11457,27 +11457,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="AL84" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="85">
@@ -11589,27 +11589,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="AL85" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="86">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="M86" t="n">
-        <v>3.18</v>
+        <v>4.7</v>
       </c>
       <c r="N86" t="n">
-        <v>2.85</v>
+        <v>1.37</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>45877.66666666666</v>
+        <v>45877.67708333334</v>
       </c>
     </row>
     <row r="87">
@@ -11853,27 +11853,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>45877.66666666666</v>
+        <v>45877.79166666666</v>
       </c>
     </row>
     <row r="88">
@@ -11985,27 +11985,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="AL88" s="3" t="n">
-        <v>45877.67708333334</v>
+        <v>45877.79166666666</v>
       </c>
     </row>
     <row r="89">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="AL98" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.83333333334</v>
       </c>
     </row>
     <row r="99">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="AL99" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.85416666666</v>
       </c>
     </row>
     <row r="100">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="AL100" s="3" t="n">
-        <v>45877.83333333334</v>
+        <v>45877.875</v>
       </c>
     </row>
     <row r="101">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45877.85416666666</v>
+        <v>45877.875</v>
       </c>
     </row>
     <row r="102">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45877.875</v>
+        <v>45877.89583333334</v>
       </c>
     </row>
     <row r="103">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14088,7 +14088,7 @@
         </is>
       </c>
       <c r="AL103" s="3" t="n">
-        <v>45877.875</v>
+        <v>45877.89930555555</v>
       </c>
     </row>
     <row r="104">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14220,270 +14220,6 @@
         </is>
       </c>
       <c r="AL104" s="3" t="n">
-        <v>45877.89583333334</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>45877</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL105" s="3" t="n">
-        <v>45877.89930555555</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>45877</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL106" s="3" t="n">
         <v>45877.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL104"/>
+  <dimension ref="A1:AL103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.83</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>1.21</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>1.21</v>
       </c>
       <c r="M26" t="n">
-        <v>3.03</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.17</v>
+        <v>3.81</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="M42" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="M63" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="M79" t="n">
-        <v>3.3</v>
+        <v>3.99</v>
       </c>
       <c r="N79" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11325,27 +11325,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11448,7 +11448,7 @@
         </is>
       </c>
       <c r="AL83" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="84">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11589,12 +11589,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.47</v>
+        <v>7.4</v>
       </c>
       <c r="M85" t="n">
-        <v>3.18</v>
+        <v>4.7</v>
       </c>
       <c r="N85" t="n">
-        <v>2.85</v>
+        <v>1.37</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="AL85" s="3" t="n">
-        <v>45877.66666666666</v>
+        <v>45877.67708333334</v>
       </c>
     </row>
     <row r="86">
@@ -11721,27 +11721,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>7.4</v>
+        <v>2.11</v>
       </c>
       <c r="M86" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="N86" t="n">
-        <v>1.37</v>
+        <v>3.6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11804,16 +11804,16 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>45877.67708333334</v>
+        <v>45877.79166666666</v>
       </c>
     </row>
     <row r="87">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13296,7 +13296,7 @@
         </is>
       </c>
       <c r="AL97" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.83333333334</v>
       </c>
     </row>
     <row r="98">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="AL98" s="3" t="n">
-        <v>45877.83333333334</v>
+        <v>45877.85416666666</v>
       </c>
     </row>
     <row r="99">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="AL99" s="3" t="n">
-        <v>45877.85416666666</v>
+        <v>45877.875</v>
       </c>
     </row>
     <row r="100">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45877.875</v>
+        <v>45877.89583333334</v>
       </c>
     </row>
     <row r="102">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45877.89583333334</v>
+        <v>45877.89930555555</v>
       </c>
     </row>
     <row r="103">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14088,138 +14088,6 @@
         </is>
       </c>
       <c r="AL103" s="3" t="n">
-        <v>45877.89930555555</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>45877</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL104" s="3" t="n">
         <v>45877.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>1.83</v>
       </c>
       <c r="M15" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
         <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.21</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>3.03</v>
       </c>
       <c r="N26" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.81</v>
+        <v>3.17</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.17</v>
+        <v>3.81</v>
       </c>
       <c r="M37" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N63" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M82" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N82" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB94" t="n">
         <v>0</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.83</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>1.21</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.43</v>
+        <v>2.45</v>
       </c>
       <c r="M69" t="n">
-        <v>3.99</v>
+        <v>3.31</v>
       </c>
       <c r="N69" t="n">
-        <v>5.8</v>
+        <v>2.45</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="M74" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="N74" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12200,10 +12200,10 @@
         <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
         <v>0</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G96" t="n">

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N4" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>1.83</v>
       </c>
       <c r="M15" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="M75" t="n">
-        <v>3.99</v>
+        <v>3.3</v>
       </c>
       <c r="N75" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12200,10 +12200,10 @@
         <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB94" t="n">
         <v>0</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>1.21</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.21</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>6.5</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>7.3</v>
+        <v>3.29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,16 +4418,16 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="M47" t="n">
         <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
         <v>0</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13124,10 +13124,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.21</v>
+        <v>2.46</v>
       </c>
       <c r="M32" t="n">
-        <v>6.5</v>
+        <v>3.03</v>
       </c>
       <c r="N32" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13124,10 +13124,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N4" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.21</v>
+        <v>2.46</v>
       </c>
       <c r="M27" t="n">
-        <v>6.5</v>
+        <v>3.03</v>
       </c>
       <c r="N27" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,16 +4022,16 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N68" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="M71" t="n">
-        <v>3.31</v>
+        <v>3.99</v>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>5.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="M73" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="N73" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12332,10 +12332,10 @@
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="M27" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.17</v>
+        <v>3.81</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.81</v>
+        <v>3.17</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="M42" t="n">
         <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.43</v>
+        <v>2.45</v>
       </c>
       <c r="M71" t="n">
-        <v>3.99</v>
+        <v>3.31</v>
       </c>
       <c r="N71" t="n">
-        <v>5.8</v>
+        <v>2.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12332,10 +12332,10 @@
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13124,10 +13124,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL103"/>
+  <dimension ref="A1:AL104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N4" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="M16" t="n">
         <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="M26" t="n">
-        <v>3.77</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.81</v>
+        <v>3.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.17</v>
+        <v>3.81</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.59</v>
+        <v>5.7</v>
       </c>
       <c r="M65" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="N65" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N67" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="M69" t="n">
-        <v>3.18</v>
+        <v>3.99</v>
       </c>
       <c r="N69" t="n">
-        <v>3.09</v>
+        <v>5.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="M80" t="n">
-        <v>3.61</v>
+        <v>3.18</v>
       </c>
       <c r="N80" t="n">
-        <v>3.63</v>
+        <v>3.09</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="M81" t="n">
-        <v>3.99</v>
+        <v>3.67</v>
       </c>
       <c r="N81" t="n">
-        <v>5.8</v>
+        <v>2.94</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11936,10 +11936,10 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB87" t="n">
         <v>0</v>
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13124,10 +13124,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>
@@ -13305,12 +13305,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="AL98" s="3" t="n">
-        <v>45877.85416666666</v>
+        <v>45877.83333333334</v>
       </c>
     </row>
     <row r="99">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="AL99" s="3" t="n">
-        <v>45877.875</v>
+        <v>45877.85416666666</v>
       </c>
     </row>
     <row r="100">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45877.89583333334</v>
+        <v>45877.875</v>
       </c>
     </row>
     <row r="102">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45877.89930555555</v>
+        <v>45877.89583333334</v>
       </c>
     </row>
     <row r="103">
@@ -13965,129 +13965,261 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M103" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N103" t="n">
+        <v>5</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL103" s="3" t="n">
+        <v>45877.89930555555</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="inlineStr">
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L103" t="n">
+      <c r="L104" t="n">
         <v>6.95</v>
       </c>
-      <c r="M103" t="n">
+      <c r="M104" t="n">
         <v>4.5</v>
       </c>
-      <c r="N103" t="n">
+      <c r="N104" t="n">
         <v>1.41</v>
       </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB103" t="n">
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC103" t="n">
+      <c r="AC104" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL103" s="3" t="n">
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL104" s="3" t="n">
         <v>45877.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL104"/>
+  <dimension ref="A1:AL103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -947,43 +947,43 @@
         <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB4" t="n">
         <v>1.8</v>
@@ -992,22 +992,22 @@
         <v>1.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1079,67 +1079,67 @@
         <v>6.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2085,27 +2085,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2168,34 +2168,34 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45877.45833333334</v>
+        <v>45877.5</v>
       </c>
     </row>
     <row r="14">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="N15" t="n">
-        <v>1.21</v>
+        <v>6.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3141,27 +3141,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45877.5</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,40 +3974,40 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.46</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>3.03</v>
+        <v>4.21</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>5.56</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4857,27 +4857,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45877.55208333334</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.17</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="N35" t="n">
-        <v>2.11</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -5121,27 +5121,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45877.5625</v>
+        <v>45877.55208333334</v>
       </c>
     </row>
     <row r="37">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.31</v>
+        <v>3.17</v>
       </c>
       <c r="M38" t="n">
-        <v>3.07</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>3.21</v>
+        <v>2.11</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="39">
@@ -5517,27 +5517,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45877.58333333334</v>
+        <v>45877.5625</v>
       </c>
     </row>
     <row r="40">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5781,27 +5781,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="M41" t="n">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5913,27 +5913,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -6177,27 +6177,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -6309,27 +6309,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>18</v>
       </c>
       <c r="N45" t="n">
-        <v>3.3</v>
+        <v>41</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="AL45" s="3" t="n">
-        <v>45877.60416666666</v>
+        <v>45877.58333333334</v>
       </c>
     </row>
     <row r="46">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N46" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6500,58 +6500,58 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7028,58 +7028,58 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>45877.61458333334</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="52">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7292,58 +7292,58 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="53">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="AL53" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="54">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="AL54" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="55">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7688,58 +7688,58 @@
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="AL55" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.60416666666</v>
       </c>
     </row>
     <row r="56">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="AL56" s="3" t="n">
-        <v>45877.625</v>
+        <v>45877.61458333334</v>
       </c>
     </row>
     <row r="57">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="N57" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,76 +8066,76 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,76 +8198,76 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,76 +8462,76 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -8553,12 +8553,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,76 +8594,76 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>45877.63541666666</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="63">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="N63" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8768,16 +8768,16 @@
         <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="AL63" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="64">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,76 +8858,76 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="AL64" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="65">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="AL65" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="66">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,76 +9122,76 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="AL66" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="67">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.59</v>
+        <v>2.79</v>
       </c>
       <c r="M67" t="n">
-        <v>3.62</v>
+        <v>3.29</v>
       </c>
       <c r="N67" t="n">
-        <v>4.7</v>
+        <v>2.09</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="AL67" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="68">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,76 +9386,76 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>45877.64583333334</v>
+        <v>45877.625</v>
       </c>
     </row>
     <row r="69">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,76 +9518,76 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.43</v>
+        <v>2.39</v>
       </c>
       <c r="M69" t="n">
-        <v>3.99</v>
+        <v>3.08</v>
       </c>
       <c r="N69" t="n">
-        <v>5.8</v>
+        <v>2.66</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.63541666666</v>
       </c>
     </row>
     <row r="70">
@@ -9609,27 +9609,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.63541666666</v>
       </c>
     </row>
     <row r="71">
@@ -9741,27 +9741,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="AL71" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="72">
@@ -9873,27 +9873,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,76 +9914,76 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AL72" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="73">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="M73" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>3.63</v>
+        <v>4.2</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="AL73" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="74">
@@ -10137,27 +10137,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,40 +10178,40 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -10226,22 +10226,22 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH74" t="n">
         <v>0</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="AL74" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="75">
@@ -10269,27 +10269,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,76 +10310,76 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         </is>
       </c>
       <c r="AL75" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="76">
@@ -10401,27 +10401,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="AL76" s="3" t="n">
-        <v>45877.65625</v>
+        <v>45877.64583333334</v>
       </c>
     </row>
     <row r="77">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,76 +10574,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="M77" t="n">
-        <v>3.31</v>
+        <v>4.3</v>
       </c>
       <c r="N77" t="n">
-        <v>2.45</v>
+        <v>7.9</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.31</v>
+        <v>2.07</v>
       </c>
       <c r="M78" t="n">
-        <v>4.3</v>
+        <v>3.18</v>
       </c>
       <c r="N78" t="n">
-        <v>7.9</v>
+        <v>3.09</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB78" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG78" t="n">
         <v>1.87</v>
       </c>
-      <c r="AC78" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>0</v>
-      </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,76 +10838,76 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.22</v>
+        <v>1.43</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>3.99</v>
       </c>
       <c r="N79" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,76 +10970,76 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="M80" t="n">
-        <v>3.18</v>
+        <v>3.67</v>
       </c>
       <c r="N80" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,76 +11102,76 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="M81" t="n">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11252,58 +11252,58 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -11325,12 +11325,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,76 +11366,76 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         </is>
       </c>
       <c r="AL83" s="3" t="n">
-        <v>45877.66666666666</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="84">
@@ -11457,27 +11457,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.47</v>
+        <v>1.28</v>
       </c>
       <c r="M84" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="N84" t="n">
-        <v>2.85</v>
+        <v>7.7</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11516,58 +11516,58 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI84" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="AL84" s="3" t="n">
-        <v>45877.66666666666</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="85">
@@ -11589,27 +11589,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,76 +11630,76 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>7.4</v>
+        <v>2.53</v>
       </c>
       <c r="M85" t="n">
-        <v>4.7</v>
+        <v>3.47</v>
       </c>
       <c r="N85" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V85" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X85" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AE85" t="n">
         <v>1.37</v>
       </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>0</v>
-      </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="AL85" s="3" t="n">
-        <v>45877.67708333334</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="86">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11780,58 +11780,58 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI86" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="87">
@@ -11853,27 +11853,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,76 +11894,76 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="M87" t="n">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="N87" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI87" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.65625</v>
       </c>
     </row>
     <row r="88">
@@ -11985,12 +11985,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,76 +12026,76 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="AL88" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="89">
@@ -12117,27 +12117,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="AL89" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="90">
@@ -12249,12 +12249,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,76 +12290,76 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI90" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="AL90" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="91">
@@ -12381,27 +12381,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,76 +12422,76 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI91" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="AL91" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.66666666666</v>
       </c>
     </row>
     <row r="92">
@@ -12513,27 +12513,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,76 +12554,76 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI92" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         </is>
       </c>
       <c r="AL92" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.67708333334</v>
       </c>
     </row>
     <row r="93">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,76 +12686,76 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI93" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,76 +12818,76 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI94" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -12909,12 +12909,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13032,7 +13032,7 @@
         </is>
       </c>
       <c r="AL95" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.83333333334</v>
       </c>
     </row>
     <row r="96">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,76 +13082,76 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI96" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         </is>
       </c>
       <c r="AL96" s="3" t="n">
-        <v>45877.79166666666</v>
+        <v>45877.83333333334</v>
       </c>
     </row>
     <row r="97">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13296,7 +13296,7 @@
         </is>
       </c>
       <c r="AL97" s="3" t="n">
-        <v>45877.83333333334</v>
+        <v>45877.85416666666</v>
       </c>
     </row>
     <row r="98">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,76 +13346,76 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="AL98" s="3" t="n">
-        <v>45877.83333333334</v>
+        <v>45877.875</v>
       </c>
     </row>
     <row r="99">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13496,58 +13496,58 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI99" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="AL99" s="3" t="n">
-        <v>45877.85416666666</v>
+        <v>45877.875</v>
       </c>
     </row>
     <row r="100">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45877.875</v>
+        <v>45877.89583333334</v>
       </c>
     </row>
     <row r="102">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,76 +13874,76 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V102" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI102" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45877.89583333334</v>
+        <v>45877.89930555555</v>
       </c>
     </row>
     <row r="103">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.72</v>
+        <v>7.4</v>
       </c>
       <c r="M103" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N103" t="n">
-        <v>5</v>
+        <v>1.33</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14024,58 +14024,58 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI103" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -14088,138 +14088,6 @@
         </is>
       </c>
       <c r="AL103" s="3" t="n">
-        <v>45877.89930555555</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>45877</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="M104" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N104" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL104" s="3" t="n">
         <v>45877.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.42</v>
       </c>
-      <c r="V4" t="n">
-        <v>6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD5" t="n">
         <v>3.1</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AE5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.12</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.15</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>15</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>1.21</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2168,34 +2168,34 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2564,34 +2564,34 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>7.85</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.46</v>
+        <v>1.58</v>
       </c>
       <c r="M22" t="n">
-        <v>3.03</v>
+        <v>3.99</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>5.02</v>
       </c>
       <c r="O22" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="P22" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.98</v>
+        <v>2.95</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>7.3</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
         <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.55</v>
+        <v>5.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>4.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.48</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.94</v>
+        <v>2.78</v>
       </c>
       <c r="M24" t="n">
         <v>3.11</v>
       </c>
       <c r="N24" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="P24" t="n">
-        <v>7.1</v>
+        <v>8.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,40 +3710,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3770,10 +3770,10 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,40 +3974,40 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="M27" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>2.92</v>
       </c>
       <c r="O27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M29" t="n">
-        <v>4.21</v>
+        <v>4.08</v>
       </c>
       <c r="N29" t="n">
-        <v>5.56</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>1.49</v>
@@ -4256,46 +4256,46 @@
         <v>2.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="U29" t="n">
         <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.84</v>
+        <v>3.08</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AF29" t="n">
         <v>1.75</v>
@@ -4307,7 +4307,7 @@
         <v>5.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.56</v>
+        <v>4.16</v>
       </c>
       <c r="M31" t="n">
-        <v>3.77</v>
+        <v>3.38</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7</v>
+        <v>1.91</v>
       </c>
       <c r="O31" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.81</v>
+        <v>3.17</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="O37" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>6.3</v>
+        <v>5.55</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AD37" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.17</v>
+        <v>3.81</v>
       </c>
       <c r="M38" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T38" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>5.55</v>
+        <v>6.3</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6089,10 +6089,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6152,10 +6152,10 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M45" t="n">
-        <v>18</v>
+        <v>3.11</v>
       </c>
       <c r="N45" t="n">
-        <v>41</v>
+        <v>2.34</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6500,58 +6500,58 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7028,58 +7028,58 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R52" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z52" t="n">
         <v>1.3</v>
       </c>
-      <c r="V52" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AA52" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.7</v>
+        <v>3.51</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="n">
-        <v>8</v>
+        <v>6.45</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="M54" t="n">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="N54" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="O54" t="n">
         <v>1.92</v>
@@ -7562,37 +7562,37 @@
         <v>3.2</v>
       </c>
       <c r="T54" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="U54" t="n">
         <v>1.55</v>
       </c>
       <c r="V54" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X54" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>13.4</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
         <v>1.17</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.33</v>
+        <v>4.63</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AE54" t="n">
         <v>1.46</v>
@@ -7601,13 +7601,13 @@
         <v>1.45</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N55" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R55" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="S55" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T55" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="U55" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="V55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X55" t="n">
         <v>1.08</v>
       </c>
-      <c r="X55" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y55" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.34</v>
+        <v>4.4</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH55" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,76 +7934,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.72</v>
+        <v>1.88</v>
       </c>
       <c r="M57" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="O57" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S57" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="T57" t="n">
-        <v>3.19</v>
+        <v>2.37</v>
       </c>
       <c r="U57" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="V57" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="W57" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X57" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.6</v>
+        <v>2.46</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,76 +8066,76 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="M58" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N58" t="n">
-        <v>5.83</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="P58" t="n">
         <v>11</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R58" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="S58" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="U58" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="V58" t="n">
-        <v>5.45</v>
+        <v>3.9</v>
       </c>
       <c r="W58" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X58" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
         <v>12</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AA58" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AH58" t="n">
-        <v>4.75</v>
+        <v>3.72</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,76 +8198,76 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.66</v>
+        <v>1.42</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="N59" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="O59" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="P59" t="n">
         <v>11</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="R59" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S59" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T59" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="U59" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V59" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="W59" t="n">
         <v>1.12</v>
       </c>
       <c r="X59" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y59" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AD59" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AG59" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH59" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,76 +8462,76 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="M61" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="P61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="R61" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S61" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T61" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="V61" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="W61" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X61" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y61" t="n">
-        <v>12.9</v>
+        <v>7.3</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA61" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.35</v>
+        <v>3.9</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="n">
-        <v>4.15</v>
+        <v>7</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,76 +8594,76 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="M62" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>3.62</v>
+        <v>2.63</v>
       </c>
       <c r="O62" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="P62" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="R62" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S62" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T62" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U62" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V62" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="W62" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X62" t="n">
         <v>1.03</v>
       </c>
       <c r="Y62" t="n">
-        <v>15</v>
+        <v>12.9</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AA62" t="n">
         <v>4.33</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AE62" t="n">
         <v>1.5</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG62" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH62" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="M63" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,28 +8858,28 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.86</v>
+        <v>3.9</v>
       </c>
       <c r="M64" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N64" t="n">
-        <v>3.95</v>
+        <v>1.67</v>
       </c>
       <c r="O64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S64" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T64" t="n">
         <v>2.38</v>
@@ -8888,46 +8888,46 @@
         <v>1.53</v>
       </c>
       <c r="V64" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="W64" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X64" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD64" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH64" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,76 +8990,76 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,76 +9122,76 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="M66" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V66" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH66" t="n">
         <v>5</v>
       </c>
-      <c r="O66" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P66" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="AI66" t="n">
         <v>1.13</v>
-      </c>
-      <c r="S66" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V66" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1.25</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,76 +9386,76 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="M68" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="N68" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="O68" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="P68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q68" t="n">
         <v>1.91</v>
       </c>
       <c r="R68" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S68" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U68" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V68" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="W68" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X68" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y68" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG68" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD68" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH68" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,76 +9518,76 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,76 +9650,76 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,76 +9782,76 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.7</v>
+        <v>6.25</v>
       </c>
       <c r="M71" t="n">
-        <v>3.61</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,76 +9914,76 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.29</v>
+        <v>5.7</v>
       </c>
       <c r="M72" t="n">
-        <v>3.29</v>
+        <v>3.61</v>
       </c>
       <c r="N72" t="n">
-        <v>3.09</v>
+        <v>1.5</v>
       </c>
       <c r="O72" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S72" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="T72" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="U72" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V72" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W72" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X72" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AD72" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG72" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG72" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH72" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,40 +10046,40 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="N73" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X73" t="n">
         <v>0</v>
@@ -10094,22 +10094,22 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,40 +10178,40 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="M74" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="N74" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="O74" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -10226,22 +10226,22 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,76 +10310,76 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>6.25</v>
+        <v>2.29</v>
       </c>
       <c r="M75" t="n">
-        <v>5</v>
+        <v>3.29</v>
       </c>
       <c r="N75" t="n">
-        <v>1.33</v>
+        <v>3.09</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="P75" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="R75" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S75" t="n">
-        <v>3.75</v>
+        <v>3.01</v>
       </c>
       <c r="T75" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V75" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG75" t="n">
         <v>2.1</v>
       </c>
-      <c r="U75" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V75" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W75" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>2</v>
-      </c>
       <c r="AH75" t="n">
-        <v>3.85</v>
+        <v>6.49</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,40 +10442,40 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="M76" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="N76" t="n">
-        <v>4.7</v>
+        <v>4.23</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10502,10 +10502,10 @@
         <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH76" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,76 +10574,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.31</v>
+        <v>2.15</v>
       </c>
       <c r="M77" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>7.9</v>
+        <v>3.15</v>
       </c>
       <c r="O77" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="P77" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="R77" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U77" t="n">
         <v>1.36</v>
       </c>
-      <c r="S77" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T77" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U77" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V77" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W77" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X77" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y77" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA77" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD77" t="n">
         <v>3.4</v>
       </c>
-      <c r="AB77" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AE77" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AH77" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.07</v>
+        <v>2.61</v>
       </c>
       <c r="M78" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>3.09</v>
+        <v>2.39</v>
       </c>
       <c r="O78" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="R78" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S78" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T78" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U78" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V78" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="W78" t="n">
         <v>1.08</v>
       </c>
       <c r="X78" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y78" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AA78" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD78" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,37 +10838,37 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="M79" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="O79" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="P79" t="n">
-        <v>12.25</v>
+        <v>11.75</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="R79" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T79" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U79" t="n">
         <v>1.42</v>
       </c>
       <c r="V79" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="W79" t="n">
         <v>1.1</v>
@@ -10883,31 +10883,31 @@
         <v>1.23</v>
       </c>
       <c r="AA79" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AD79" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AH79" t="n">
-        <v>6.1</v>
+        <v>5.82</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,76 +10970,76 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.97</v>
+        <v>2.67</v>
       </c>
       <c r="M80" t="n">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
-        <v>2.94</v>
+        <v>2.22</v>
       </c>
       <c r="O80" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="P80" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="R80" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S80" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T80" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="U80" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V80" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W80" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X80" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA80" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH80" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,76 +11234,76 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="M82" t="n">
-        <v>3.13</v>
+        <v>3.61</v>
       </c>
       <c r="N82" t="n">
-        <v>2.79</v>
+        <v>3.63</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R82" t="n">
         <v>1.33</v>
       </c>
       <c r="S82" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T82" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U82" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V82" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W82" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X82" t="n">
         <v>1.05</v>
       </c>
       <c r="Y82" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Z82" t="n">
         <v>1.25</v>
       </c>
       <c r="AA82" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG82" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH82" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,76 +11366,76 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="M83" t="n">
-        <v>3.61</v>
+        <v>4.6</v>
       </c>
       <c r="N83" t="n">
-        <v>3.63</v>
+        <v>7.5</v>
       </c>
       <c r="O83" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="P83" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="R83" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S83" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T83" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="U83" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V83" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W83" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X83" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y83" t="n">
-        <v>9.5</v>
+        <v>15</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AA83" t="n">
-        <v>3.8</v>
+        <v>4.67</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG83" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH83" t="n">
-        <v>5.5</v>
+        <v>4.17</v>
       </c>
       <c r="AI83" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,76 +11498,76 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.28</v>
+        <v>2.65</v>
       </c>
       <c r="M84" t="n">
-        <v>4.9</v>
+        <v>3.32</v>
       </c>
       <c r="N84" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R84" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S84" t="n">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="T84" t="n">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="U84" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="V84" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="W84" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X84" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y84" t="n">
-        <v>15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z84" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE84" t="n">
         <v>1.18</v>
       </c>
-      <c r="AA84" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF84" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AG84" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH84" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,76 +11630,76 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="M85" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="N85" t="n">
-        <v>2.29</v>
+        <v>2.97</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R85" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S85" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T85" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="U85" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V85" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W85" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X85" t="n">
         <v>1.02</v>
       </c>
       <c r="Y85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA85" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG85" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH85" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,22 +11762,22 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="M86" t="n">
-        <v>3.53</v>
+        <v>4.25</v>
       </c>
       <c r="N86" t="n">
-        <v>3.57</v>
+        <v>8.23</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R86" t="n">
         <v>1.36</v>
@@ -11789,49 +11789,49 @@
         <v>2.62</v>
       </c>
       <c r="U86" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V86" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W86" t="n">
         <v>1.09</v>
       </c>
       <c r="X86" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y86" t="n">
         <v>10</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA86" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD86" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG86" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AH86" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,76 +11894,76 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="M87" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="N87" t="n">
-        <v>2.45</v>
+        <v>6.5</v>
       </c>
       <c r="O87" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P87" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S87" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V87" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X87" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF87" t="n">
         <v>2</v>
       </c>
-      <c r="P87" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>2</v>
-      </c>
-      <c r="R87" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S87" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T87" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U87" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V87" t="n">
-        <v>7</v>
-      </c>
-      <c r="W87" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X87" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA87" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC87" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD87" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE87" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF87" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG87" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH87" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,22 +12026,22 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N88" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O88" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="P88" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R88" t="n">
         <v>1.33</v>
@@ -12050,52 +12050,52 @@
         <v>3.25</v>
       </c>
       <c r="T88" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U88" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V88" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W88" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X88" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y88" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA88" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG88" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH88" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -12158,76 +12158,76 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,76 +12290,76 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.67</v>
+        <v>2.47</v>
       </c>
       <c r="M90" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="N90" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="O90" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="P90" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="R90" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S90" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="T90" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U90" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V90" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W90" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X90" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y90" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AA90" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC90" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="AD90" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG90" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH90" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,76 +12422,76 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.47</v>
+        <v>1.66</v>
       </c>
       <c r="M91" t="n">
-        <v>3.18</v>
+        <v>4.1</v>
       </c>
       <c r="N91" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="O91" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="P91" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="R91" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U91" t="n">
         <v>1.44</v>
       </c>
-      <c r="S91" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T91" t="n">
-        <v>3</v>
-      </c>
-      <c r="U91" t="n">
+      <c r="V91" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE91" t="n">
         <v>1.36</v>
       </c>
-      <c r="V91" t="n">
-        <v>9</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X91" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF91" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG91" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH91" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,76 +12686,76 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="M93" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="N93" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O93" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="P93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S93" t="n">
         <v>2.75</v>
       </c>
-      <c r="R93" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S93" t="n">
-        <v>2.2</v>
-      </c>
       <c r="T93" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U93" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="V93" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W93" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X93" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y93" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="AD93" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AH93" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,76 +12818,76 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="M94" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O94" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="R94" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S94" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="T94" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U94" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V94" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="W94" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X94" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y94" t="n">
-        <v>11</v>
+        <v>6.25</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AA94" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AG94" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AH94" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI94" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,76 +12950,76 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI95" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,76 +13082,76 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,76 +13346,76 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="M98" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="O98" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S98" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V98" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W98" t="n">
         <v>1.07</v>
       </c>
       <c r="X98" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y98" t="n">
         <v>8</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AA98" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD98" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG98" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH98" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AI98" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13496,58 +13496,58 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,76 +13610,76 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI100" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M102" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O102" t="n">
         <v>1.53</v>
@@ -13892,58 +13892,58 @@
         <v>3.3</v>
       </c>
       <c r="R102" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S102" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="T102" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="U102" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V102" t="n">
         <v>7.8</v>
       </c>
       <c r="W102" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X102" t="n">
         <v>1.11</v>
       </c>
       <c r="Y102" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD102" t="n">
         <v>5.1</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF102" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AG102" t="n">
         <v>1.55</v>
       </c>
       <c r="AH102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI102" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -14024,58 +14024,58 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S103" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T103" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U103" t="n">
         <v>1.4</v>
       </c>
-      <c r="S103" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T103" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U103" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V103" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="W103" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X103" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y103" t="n">
-        <v>7.95</v>
+        <v>10</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD103" t="n">
         <v>2.97</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG103" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AH103" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI103" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -806,37 +806,37 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q3" t="n">
         <v>1.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
         <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="W3" t="n">
         <v>1.13</v>
@@ -848,34 +848,34 @@
         <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2564,34 +2564,34 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>7.85</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,40 +3050,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -3092,34 +3092,34 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>3.62</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="O21" t="n">
         <v>1.62</v>
@@ -3230,10 +3230,10 @@
         <v>3.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD21" t="n">
         <v>3</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.37</v>
+        <v>4.16</v>
       </c>
       <c r="M23" t="n">
-        <v>4.75</v>
+        <v>3.38</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>1.91</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>19</v>
+        <v>7.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>1.67</v>
       </c>
       <c r="R23" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>4.45</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.85</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.78</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>3.11</v>
+        <v>3.77</v>
       </c>
       <c r="N24" t="n">
-        <v>2.45</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="P24" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.98</v>
+        <v>2.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
         <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.25</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF24" t="n">
         <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.75</v>
+        <v>5.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.44</v>
@@ -3764,10 +3764,10 @@
         <v>2.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF25" t="n">
         <v>1.62</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="M26" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="M29" t="n">
-        <v>4.08</v>
+        <v>6.5</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S29" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC29" t="n">
         <v>3.1</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AD29" t="n">
-        <v>3.08</v>
+        <v>1.82</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>4.08</v>
       </c>
       <c r="N30" t="n">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.16</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="N31" t="n">
-        <v>1.91</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>7.1</v>
+        <v>21</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>7.75</v>
+        <v>4.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AA31" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>6.3</v>
+        <v>3.35</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,76 +6614,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,76 +7010,76 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,76 +7142,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,76 +7274,76 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,76 +7406,76 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M54" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N54" t="n">
-        <v>2.47</v>
+        <v>4.1</v>
       </c>
       <c r="O54" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="P54" t="n">
-        <v>15.5</v>
+        <v>6.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.89</v>
+        <v>2.73</v>
       </c>
       <c r="R54" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="S54" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="T54" t="n">
-        <v>2.25</v>
+        <v>3.48</v>
       </c>
       <c r="U54" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W54" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y54" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.63</v>
+        <v>2.6</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH54" t="n">
-        <v>4.33</v>
+        <v>9</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,76 +7670,76 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="M55" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="N55" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="O55" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="P55" t="n">
-        <v>6.45</v>
+        <v>15.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.73</v>
+        <v>1.89</v>
       </c>
       <c r="R55" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="S55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V55" t="n">
+        <v>5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD55" t="n">
         <v>2.4</v>
       </c>
-      <c r="T55" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V55" t="n">
-        <v>9</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AE55" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>9</v>
+        <v>4.33</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,73 +7934,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.88</v>
+        <v>2.71</v>
       </c>
       <c r="M57" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N57" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="O57" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="P57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="R57" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T57" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="U57" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V57" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="W57" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X57" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y57" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AA57" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.46</v>
+        <v>2.85</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH57" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AI57" t="n">
         <v>1.14</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,76 +8066,76 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="M58" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N58" t="n">
         <v>4.5</v>
       </c>
-      <c r="N58" t="n">
-        <v>5</v>
-      </c>
       <c r="O58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AA58" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,76 +8330,76 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="M60" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="O60" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.83</v>
+        <v>2.37</v>
       </c>
       <c r="R60" t="n">
         <v>1.25</v>
       </c>
       <c r="S60" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T60" t="n">
         <v>2.35</v>
       </c>
       <c r="U60" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="V60" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W60" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X60" t="n">
         <v>1.03</v>
       </c>
       <c r="Y60" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AA60" t="n">
-        <v>4.33</v>
+        <v>4.94</v>
       </c>
       <c r="AB60" t="n">
         <v>1.57</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD60" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH60" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,76 +8462,76 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="M61" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S61" t="n">
         <v>3</v>
       </c>
-      <c r="N61" t="n">
+      <c r="T61" t="n">
         <v>2.5</v>
       </c>
-      <c r="O61" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P61" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T61" t="n">
-        <v>3</v>
-      </c>
       <c r="U61" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="V61" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="W61" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X61" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y61" t="n">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.83</v>
+        <v>3.8</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,76 +8594,76 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,76 +8726,76 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="M63" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="N63" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z63" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF63" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA63" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,76 +8858,76 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.9</v>
+        <v>1.88</v>
       </c>
       <c r="M64" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O64" t="n">
         <v>1.67</v>
       </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R64" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S64" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T64" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="U64" t="n">
         <v>1.53</v>
       </c>
       <c r="V64" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W64" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,76 +8990,76 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="M65" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N65" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="O65" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="P65" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="R65" t="n">
         <v>1.25</v>
       </c>
       <c r="S65" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T65" t="n">
         <v>2.35</v>
       </c>
       <c r="U65" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V65" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W65" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X65" t="n">
         <v>1.03</v>
       </c>
       <c r="Y65" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.94</v>
+        <v>4.33</v>
       </c>
       <c r="AB65" t="n">
         <v>1.57</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AD65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG65" t="n">
         <v>2.4</v>
       </c>
-      <c r="AE65" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH65" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,76 +9122,76 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R66" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T66" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V66" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD66" t="n">
         <v>2.5</v>
       </c>
-      <c r="U66" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V66" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X66" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AE66" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AH66" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,76 +9254,76 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,76 +9386,76 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.71</v>
+        <v>3.9</v>
       </c>
       <c r="M68" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N68" t="n">
-        <v>2.52</v>
+        <v>1.67</v>
       </c>
       <c r="O68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T68" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U68" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V68" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="W68" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X68" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AC68" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD68" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG68" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,76 +9518,76 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,76 +9650,76 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,76 +9782,76 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>6.25</v>
+        <v>1.7</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="O71" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S71" t="n">
         <v>3</v>
       </c>
-      <c r="P71" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S71" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T71" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U71" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V71" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W71" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X71" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG71" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH71" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,64 +10046,64 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="M73" t="n">
-        <v>4.33</v>
+        <v>3.29</v>
       </c>
       <c r="N73" t="n">
-        <v>5.8</v>
+        <v>3.09</v>
       </c>
       <c r="O73" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P73" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U73" t="n">
         <v>1.4</v>
       </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S73" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T73" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V73" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="W73" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="AD73" t="n">
-        <v>2.25</v>
+        <v>3.36</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AF73" t="n">
         <v>1.67</v>
@@ -10112,10 +10112,10 @@
         <v>2.1</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="AI73" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,76 +10178,76 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.75</v>
+        <v>6.25</v>
       </c>
       <c r="M74" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="N74" t="n">
-        <v>3.9</v>
+        <v>1.33</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,76 +10310,76 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.29</v>
+        <v>1.59</v>
       </c>
       <c r="M75" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="N75" t="n">
-        <v>3.09</v>
+        <v>4.7</v>
       </c>
       <c r="O75" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,70 +10442,70 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="M76" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="N76" t="n">
-        <v>4.23</v>
+        <v>4.8</v>
       </c>
       <c r="O76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF76" t="n">
         <v>1.67</v>
       </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S76" t="n">
-        <v>3</v>
-      </c>
-      <c r="T76" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V76" t="n">
-        <v>7</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG76" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,76 +10574,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P77" t="n">
-        <v>8</v>
+        <v>11.75</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R77" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S77" t="n">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="T77" t="n">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="U77" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V77" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="W77" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X77" t="n">
         <v>1.02</v>
       </c>
       <c r="Y77" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AA77" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="AB77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC77" t="n">
         <v>1.93</v>
       </c>
-      <c r="AC77" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD77" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AH77" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,76 +10706,76 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.61</v>
+        <v>1.3</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N78" t="n">
-        <v>2.39</v>
+        <v>7.5</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="R78" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S78" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T78" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U78" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="V78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W78" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X78" t="n">
         <v>1</v>
       </c>
       <c r="Y78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AA78" t="n">
-        <v>3.28</v>
+        <v>4.67</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF78" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD78" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG78" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="n">
-        <v>6.5</v>
+        <v>4.17</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,76 +10838,76 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="M79" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="O79" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="P79" t="n">
-        <v>11.75</v>
+        <v>9.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="R79" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S79" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T79" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U79" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V79" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="W79" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X79" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y79" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AA79" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AD79" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH79" t="n">
-        <v>5.82</v>
+        <v>6.75</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,76 +10970,76 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N80" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="O80" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="P80" t="n">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="R80" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S80" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T80" t="n">
         <v>3.04</v>
       </c>
-      <c r="T80" t="n">
-        <v>2.58</v>
-      </c>
       <c r="U80" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V80" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X80" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y80" t="n">
-        <v>10.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AA80" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.81</v>
+        <v>3.82</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AH80" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,37 +11102,37 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="M81" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N81" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="O81" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P81" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S81" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T81" t="n">
         <v>2.75</v>
       </c>
       <c r="U81" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W81" t="n">
         <v>1.08</v>
@@ -11141,37 +11141,37 @@
         <v>1</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AA81" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH81" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,76 +11234,76 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="M82" t="n">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="N82" t="n">
-        <v>3.63</v>
+        <v>2.94</v>
       </c>
       <c r="O82" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P82" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="R82" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S82" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T82" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="U82" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V82" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W82" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X82" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y82" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA82" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG82" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH82" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,76 +11366,76 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.3</v>
+        <v>2.67</v>
       </c>
       <c r="M83" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>7.5</v>
+        <v>2.22</v>
       </c>
       <c r="O83" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="P83" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="R83" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S83" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="T83" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="U83" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V83" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W83" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X83" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y83" t="n">
-        <v>15</v>
+        <v>10.9</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA83" t="n">
-        <v>4.67</v>
+        <v>3.8</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.28</v>
+        <v>2.81</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG83" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH83" t="n">
-        <v>4.17</v>
+        <v>5.5</v>
       </c>
       <c r="AI83" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,76 +11498,76 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="M84" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O84" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P84" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="R84" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S84" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="T84" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="U84" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V84" t="n">
         <v>7</v>
       </c>
       <c r="W84" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X84" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y84" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AD84" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG84" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,76 +11630,76 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="M85" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="N85" t="n">
-        <v>2.97</v>
+        <v>8.23</v>
       </c>
       <c r="O85" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="P85" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q85" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S85" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V85" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X85" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF85" t="n">
         <v>2.1</v>
       </c>
-      <c r="R85" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S85" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T85" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U85" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V85" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W85" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X85" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG85" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AH85" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,43 +11762,43 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M86" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="N86" t="n">
-        <v>8.23</v>
+        <v>5.8</v>
       </c>
       <c r="O86" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="P86" t="n">
-        <v>9.5</v>
+        <v>12.25</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="R86" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S86" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T86" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U86" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V86" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="W86" t="n">
         <v>1.09</v>
       </c>
       <c r="X86" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y86" t="n">
         <v>10</v>
@@ -11807,31 +11807,31 @@
         <v>1.25</v>
       </c>
       <c r="AA86" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC86" t="n">
         <v>1.85</v>
       </c>
       <c r="AD86" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AH86" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,76 +11894,76 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="M87" t="n">
-        <v>4</v>
+        <v>3.61</v>
       </c>
       <c r="N87" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P87" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V87" t="n">
         <v>6.5</v>
       </c>
-      <c r="O87" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P87" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R87" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S87" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T87" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U87" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V87" t="n">
-        <v>6.2</v>
-      </c>
       <c r="W87" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X87" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y87" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z87" t="n">
         <v>1.25</v>
       </c>
       <c r="AA87" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AD87" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF87" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG87" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AH87" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,76 +12158,76 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.17</v>
+        <v>1.66</v>
       </c>
       <c r="M89" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N89" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="O89" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="R89" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S89" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T89" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="U89" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="V89" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA89" t="n">
         <v>4</v>
       </c>
-      <c r="W89" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X89" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA89" t="n">
+      <c r="AB89" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH89" t="n">
         <v>5.5</v>
       </c>
-      <c r="AB89" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AI89" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,76 +12290,76 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.47</v>
+        <v>1.17</v>
       </c>
       <c r="M90" t="n">
-        <v>3.18</v>
+        <v>7.6</v>
       </c>
       <c r="N90" t="n">
-        <v>2.85</v>
+        <v>17</v>
       </c>
       <c r="O90" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P90" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V90" t="n">
+        <v>4</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD90" t="n">
         <v>2.05</v>
       </c>
-      <c r="R90" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S90" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T90" t="n">
-        <v>3</v>
-      </c>
-      <c r="U90" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V90" t="n">
-        <v>9</v>
-      </c>
-      <c r="W90" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X90" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC90" t="n">
+      <c r="AE90" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD90" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE90" t="n">
+      <c r="AF90" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI90" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AI90" t="n">
-        <v>1.08</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,76 +12422,76 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.66</v>
+        <v>2.47</v>
       </c>
       <c r="M91" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="N91" t="n">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="O91" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="P91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="R91" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S91" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="T91" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V91" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="W91" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X91" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y91" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AA91" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH91" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M98" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13373,16 +13373,16 @@
         <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V98" t="n">
         <v>7</v>
       </c>
       <c r="W98" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X98" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y98" t="n">
         <v>8</v>
@@ -13403,7 +13403,7 @@
         <v>3.58</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF98" t="n">
         <v>1.85</v>
@@ -14024,19 +14024,19 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S103" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="T103" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="U103" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V103" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="W103" t="n">
         <v>1.09</v>
@@ -14048,16 +14048,16 @@
         <v>10</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AA103" t="n">
         <v>3.6</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AD103" t="n">
         <v>2.97</v>
@@ -14066,13 +14066,13 @@
         <v>1.36</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG103" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH103" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AI103" t="n">
         <v>1.12</v>

--- a/jogos_2025-08-08.xlsx
+++ b/jogos_2025-08-08.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="M3" t="n">
-        <v>3.33</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
         <v>1.83</v>
@@ -827,7 +827,7 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
         <v>2.25</v>
@@ -839,10 +839,10 @@
         <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
         <v>13.5</v>
@@ -854,19 +854,19 @@
         <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
         <v>2.38</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.49</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.47</v>
       </c>
       <c r="AG3" t="n">
         <v>2.4</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="N4" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD4" t="n">
         <v>3.1</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="AE4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.12</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.15</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.42</v>
       </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="N15" t="n">
-        <v>7.85</v>
+        <v>1.21</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>1.17</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="U15" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="V15" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>7.85</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,40 +3050,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>15</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -3092,34 +3092,34 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.91</v>
+        <v>1.21</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>6.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.29</v>
+        <v>7.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.16</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="N23" t="n">
-        <v>1.91</v>
+        <v>5.3</v>
       </c>
       <c r="O23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.5</v>
       </c>
-      <c r="P23" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="V24" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.43</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>4.33</v>
+        <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.63</v>
+        <v>1.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.77</v>
       </c>
       <c r="N27" t="n">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>4.08</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>3.29</v>
       </c>
       <c r="O30" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="P30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="R30" t="n">
         <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W30" t="n">
         <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.75</v>
+        <v>0</v>
